--- a/data/trans_dic/IP31KM02_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_R_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>66,1%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,2; 72,1</t>
+          <t>57,62; 78,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,37; 78,22</t>
+          <t>50,73; 73,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,17; 73,2</t>
+          <t>58,4; 73,22</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>72,63%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,37; 75,41</t>
+          <t>68,4; 78,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,34; 78,09</t>
+          <t>65,03; 76,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,89; 75,29</t>
+          <t>68,64; 76,74</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,78%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,7; 74,99</t>
+          <t>60,86; 72,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,37; 72,38</t>
+          <t>62,68; 74,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,25; 71,47</t>
+          <t>63,8; 71,98</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>60,9%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,6; 60,61</t>
+          <t>56,39; 68,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,17; 68,44</t>
+          <t>53,72; 65,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,74; 62,61</t>
+          <t>56,47; 65,14</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,91%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,57; 66,46</t>
+          <t>63,43; 70,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,13; 69,39</t>
+          <t>61,57; 68,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60,07; 66,82</t>
+          <t>63,46; 68,21</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28757</t>
+          <t>25833</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31111</t>
+          <t>27121</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59868</t>
+          <t>52954</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23338; 33525</t>
+          <t>21569; 29505</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25981; 35420</t>
+          <t>21654; 31251</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53389; 67185</t>
+          <t>46790; 58665</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>184</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>110805</t>
+          <t>116601</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>132931</t>
+          <t>103134</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243736</t>
+          <t>219735</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>100943; 120121</t>
+          <t>107414; 123991</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>122538; 142083</t>
+          <t>94633; 110920</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>228282; 256921</t>
+          <t>207689; 232175</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>159</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>119581</t>
+          <t>133723</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>139937</t>
+          <t>120325</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>259518</t>
+          <t>254047</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>108522; 129794</t>
+          <t>121802; 145626</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>126146; 153794</t>
+          <t>109476; 130334</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>243854; 275555</t>
+          <t>239120; 269789</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>200</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>144873</t>
+          <t>182846</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>188508</t>
+          <t>150613</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333382</t>
+          <t>333459</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100371; 166240</t>
+          <t>164780; 200984</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>168274; 208738</t>
+          <t>137163; 167011</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>282335; 362706</t>
+          <t>309196; 356672</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>594</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>404017</t>
+          <t>459003</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>492487</t>
+          <t>401193</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>896504</t>
+          <t>860195</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>349862; 434069</t>
+          <t>435647; 481165</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>462686; 516775</t>
+          <t>380651; 420442</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>839638; 934115</t>
+          <t>828113; 890164</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM02_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_R_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman una 2ª pieza de fruta diaria o verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>69,01%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>63,54%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>66,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>57,62; 78,82</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>50,73; 73,22</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>58,4; 73,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>74,25%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>70,87%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>72,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>68,4; 78,95</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>65,03; 76,22</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>68,64; 76,74</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>66,82%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>68,89%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>67,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>60,86; 72,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>62,68; 74,62</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>63,8; 71,98</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>62,57%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>58,99%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>60,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>56,39; 68,78</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>53,72; 65,41</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>56,47; 65,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>64,9%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>65,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>63,43; 70,06</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>61,57; 68,01</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>63,46; 68,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6900828468518567</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.63543018075102</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6609673155214959</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>25833</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>27121</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52954</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5761629142089403</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.5073402147661513</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5840297933478178</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>21569; 29505</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>21654; 31251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46790; 58665</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7881536529901942</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7321880981583888</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7322484098386682</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.742482020823427</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.7087372036756531</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.7262522755046902</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>116601</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>103134</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>219735</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.6839838430282322</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.6503191903007807</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.6864387358436409</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>107414; 123991</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94633; 110920</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>207689; 232175</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7895402994517997</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.7622407506198214</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.7673678251177103</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.6681920355493126</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.6888619474004133</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6778251167269557</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>133723</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>120325</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>254047</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.6086285457210032</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.6267521905115977</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.637996140368742</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>121802; 145626</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>109476; 130334</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>239120; 269789</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.727671808015725</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.7461649430296627</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.7198249932049243</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6257123004264308</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5898603736881106</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6089938357112784</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>182846</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>150613</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>333459</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5638872497626274</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.5371855630070681</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.5646809561991815</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>164780; 200984</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>137163; 167011</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>309196; 356672</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6877824152778694</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6540806466922786</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6513864161595923</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1220</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.6682978498137183</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.6489609897872654</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.659137766976775</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>459003</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>401193</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>860195</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.6342913599103251</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.6157328787664835</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.6345546466029393</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>435647; 481165</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>380651; 420442</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>828113; 890164</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.7005650024241967</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6800986426895353</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.682101644676941</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman una 2ª pieza de fruta diaria o verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>25833</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>27121</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>52954</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>21569</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>21654</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>46790</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>29505</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>31251</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>58665</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>116601</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>103134</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>219735</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>107414</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>94633</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>207689</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>123991</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>110920</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>232175</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>158</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>133723</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>120325</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>254047</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>121802</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>109476</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>239120</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>145626</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>130334</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>269789</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>214</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>182846</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>150613</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>333459</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>164780</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>137163</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>309196</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>200984</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>167011</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>356672</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>626</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>594</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>459003</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>401193</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>860195</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>435647</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>380651</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>828113</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>481165</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>420442</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>890164</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>